--- a/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0078</v>
+        <v>0.0314</v>
       </c>
       <c r="E2">
-        <v>0.06253500000000001</v>
+        <v>0.07519999999999999</v>
       </c>
       <c r="G2">
-        <v>0.4484636328276935</v>
+        <v>0.5480475382003396</v>
       </c>
       <c r="H2">
-        <v>0.4484636328276935</v>
+        <v>0.5480475382003396</v>
       </c>
       <c r="I2">
-        <v>0.4768572539867756</v>
+        <v>0.4254668930390493</v>
       </c>
       <c r="J2">
-        <v>0.3393723156553531</v>
+        <v>0.3294447926148162</v>
       </c>
       <c r="K2">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
       <c r="L2">
-        <v>0.3368339167639051</v>
+        <v>0.2937181663837012</v>
       </c>
       <c r="M2">
-        <v>3.916</v>
+        <v>3.644</v>
       </c>
       <c r="N2">
-        <v>0.02753867791842476</v>
+        <v>0.02831390831390831</v>
       </c>
       <c r="O2">
-        <v>0.4521939953810624</v>
+        <v>0.421271676300578</v>
       </c>
       <c r="P2">
-        <v>3.916</v>
+        <v>3.644</v>
       </c>
       <c r="Q2">
-        <v>0.02753867791842476</v>
+        <v>0.02831390831390831</v>
       </c>
       <c r="R2">
-        <v>0.4521939953810624</v>
+        <v>0.421271676300578</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.83</v>
+        <v>62.33</v>
       </c>
       <c r="V2">
-        <v>0.05506329113924051</v>
+        <v>0.4843045843045843</v>
       </c>
       <c r="W2">
-        <v>0.09022300469483568</v>
+        <v>0.06822981366459627</v>
       </c>
       <c r="X2">
-        <v>0.06937387651942586</v>
+        <v>0.1129821789850635</v>
       </c>
       <c r="Y2">
-        <v>0.02084912817540982</v>
+        <v>-0.04475236532046727</v>
       </c>
       <c r="Z2">
-        <v>0.3270576262562015</v>
+        <v>0.4317548746518105</v>
       </c>
       <c r="AA2">
-        <v>0.1193302138406294</v>
+        <v>0.1109594638882298</v>
       </c>
       <c r="AB2">
-        <v>0.06937387651942586</v>
+        <v>0.1129821789850635</v>
       </c>
       <c r="AC2">
-        <v>0.04995633732120357</v>
+        <v>-0.002022715096833744</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>-7.83</v>
+        <v>-60.48</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.01417081577939487</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.01718532280538783</v>
       </c>
       <c r="AJ2">
-        <v>-0.05827193569993303</v>
+        <v>-0.8865435356200527</v>
       </c>
       <c r="AK2">
-        <v>-0.07927508352738687</v>
+        <v>-1.334510150044131</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.1397280966767372</v>
       </c>
       <c r="AP2">
-        <v>-0.6098130841121495</v>
+        <v>-4.56797583081571</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United Insurance Company Limited (DSE:UNITEDINS)</t>
+          <t>Peoples Insurance Company Limited (DSE:PEOPLESINS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0192</v>
+        <v>-0.00285</v>
       </c>
       <c r="E3">
-        <v>-0.00693</v>
+        <v>-0.0134</v>
       </c>
       <c r="G3">
-        <v>0.3792415169660678</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.3792415169660678</v>
+        <v>0.5</v>
       </c>
       <c r="I3">
-        <v>0.3912175648702595</v>
+        <v>0.3381818181818182</v>
       </c>
       <c r="J3">
-        <v>0.2814760223143457</v>
+        <v>0.1934545454545455</v>
       </c>
       <c r="K3">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="L3">
-        <v>0.281437125748503</v>
+        <v>0.1945454545454545</v>
       </c>
       <c r="M3">
-        <v>0.676</v>
+        <v>0.573</v>
       </c>
       <c r="N3">
-        <v>0.01970845481049563</v>
+        <v>0.03493902439024391</v>
       </c>
       <c r="O3">
-        <v>0.4794326241134753</v>
+        <v>0.5355140186915887</v>
       </c>
       <c r="P3">
-        <v>0.676</v>
+        <v>0.573</v>
       </c>
       <c r="Q3">
-        <v>0.01970845481049563</v>
+        <v>0.03493902439024391</v>
       </c>
       <c r="R3">
-        <v>0.4794326241134753</v>
+        <v>0.5355140186915887</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.81</v>
+        <v>14.9</v>
       </c>
       <c r="V3">
-        <v>0.08192419825072887</v>
+        <v>0.9085365853658538</v>
       </c>
       <c r="W3">
-        <v>0.07833333333333332</v>
+        <v>0.06645962732919254</v>
       </c>
       <c r="X3">
-        <v>0.06937387651942586</v>
+        <v>0.1129821789850635</v>
       </c>
       <c r="Y3">
-        <v>0.00895945681390746</v>
-      </c>
-      <c r="Z3">
-        <v>0.4686623012160897</v>
-      </c>
-      <c r="AA3">
-        <v>0.1319172003549927</v>
+        <v>-0.04652255165587099</v>
       </c>
       <c r="AB3">
-        <v>0.06937387651942586</v>
-      </c>
-      <c r="AC3">
-        <v>0.06254332383556679</v>
+        <v>0.1129821789850635</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.81</v>
+        <v>-14.9</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.08923467767545253</v>
+        <v>-9.933333333333346</v>
       </c>
       <c r="AK3">
-        <v>-0.1495476317189995</v>
+        <v>16.55555555555555</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -824,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.377450980392157</v>
+        <v>-7.163461538461538</v>
       </c>
     </row>
     <row r="4">
@@ -844,46 +835,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0348</v>
+        <v>0.0314</v>
       </c>
       <c r="E4">
-        <v>0.132</v>
+        <v>0.07519999999999999</v>
       </c>
       <c r="G4">
-        <v>0.4652173913043479</v>
+        <v>0.5621621621621622</v>
       </c>
       <c r="H4">
-        <v>0.4652173913043479</v>
+        <v>0.5621621621621622</v>
       </c>
       <c r="I4">
-        <v>0.497584541062802</v>
+        <v>0.4713513513513514</v>
       </c>
       <c r="J4">
-        <v>0.3502415458937199</v>
+        <v>0.3238499469446352</v>
       </c>
       <c r="K4">
-        <v>7.25</v>
+        <v>5.95</v>
       </c>
       <c r="L4">
-        <v>0.3502415458937198</v>
+        <v>0.3216216216216216</v>
       </c>
       <c r="M4">
-        <v>3.24</v>
+        <v>2.61</v>
       </c>
       <c r="N4">
-        <v>0.03002780352177943</v>
+        <v>0.04371859296482412</v>
       </c>
       <c r="O4">
-        <v>0.4468965517241379</v>
+        <v>0.4386554621848739</v>
       </c>
       <c r="P4">
-        <v>3.24</v>
+        <v>2.61</v>
       </c>
       <c r="Q4">
-        <v>0.03002780352177943</v>
+        <v>0.04371859296482412</v>
       </c>
       <c r="R4">
-        <v>0.4468965517241379</v>
+        <v>0.4386554621848739</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,31 +883,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.02</v>
+        <v>35.1</v>
       </c>
       <c r="V4">
-        <v>0.04652455977757182</v>
+        <v>0.5879396984924623</v>
       </c>
       <c r="W4">
-        <v>0.102112676056338</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X4">
-        <v>0.06937387651942586</v>
+        <v>0.1129821789850635</v>
       </c>
       <c r="Y4">
-        <v>0.03273879953691217</v>
+        <v>-0.04298217898506353</v>
       </c>
       <c r="Z4">
-        <v>0.3047703180212014</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AA4">
-        <v>0.1067432273262662</v>
+        <v>0.134937477893598</v>
       </c>
       <c r="AB4">
-        <v>0.06937387651942586</v>
+        <v>0.1129821789850635</v>
       </c>
       <c r="AC4">
-        <v>0.03736935080684034</v>
+        <v>0.02195529890853447</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -928,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-5.02</v>
+        <v>-35.1</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -937,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.04879471228615862</v>
+        <v>-1.426829268292683</v>
       </c>
       <c r="AK4">
-        <v>-0.06276569142285571</v>
+        <v>-1.096875</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -952,7 +943,227 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.4648148148148147</v>
+        <v>-3.852908891328211</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>United Insurance Company Limited (DSE:UNITEDINS)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0593</v>
+      </c>
+      <c r="E5">
+        <v>0.11</v>
+      </c>
+      <c r="G5">
+        <v>0.5486238532110091</v>
+      </c>
+      <c r="H5">
+        <v>0.5486238532110091</v>
+      </c>
+      <c r="I5">
+        <v>0.3577981651376146</v>
+      </c>
+      <c r="J5">
+        <v>0.299886503357609</v>
+      </c>
+      <c r="K5">
+        <v>1.63</v>
+      </c>
+      <c r="L5">
+        <v>0.2990825688073394</v>
+      </c>
+      <c r="M5">
+        <v>0.461</v>
+      </c>
+      <c r="N5">
+        <v>0.02328282828282828</v>
+      </c>
+      <c r="O5">
+        <v>0.2828220858895706</v>
+      </c>
+      <c r="P5">
+        <v>0.461</v>
+      </c>
+      <c r="Q5">
+        <v>0.02328282828282828</v>
+      </c>
+      <c r="R5">
+        <v>0.2828220858895706</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>2.59</v>
+      </c>
+      <c r="V5">
+        <v>0.1308080808080808</v>
+      </c>
+      <c r="W5">
+        <v>0.07546296296296295</v>
+      </c>
+      <c r="X5">
+        <v>0.1129821789850635</v>
+      </c>
+      <c r="Y5">
+        <v>-0.03751921602210058</v>
+      </c>
+      <c r="Z5">
+        <v>0.2900478978179882</v>
+      </c>
+      <c r="AA5">
+        <v>0.08698144988286158</v>
+      </c>
+      <c r="AB5">
+        <v>0.1129821789850635</v>
+      </c>
+      <c r="AC5">
+        <v>-0.02600072910220196</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-2.59</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1504938988959907</v>
+      </c>
+      <c r="AK5">
+        <v>-0.2250217202432667</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>-1.263414634146341</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bangladesh General Insurance Company Limited (DSE:BGIC)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>9.74</v>
+      </c>
+      <c r="V6">
+        <v>0.2969512195121952</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0.115806416668222</v>
+      </c>
+      <c r="Y6">
+        <v>-0.115806416668222</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.1133283771356361</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1133283771356361</v>
+      </c>
+      <c r="AD6">
+        <v>1.85</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1.85</v>
+      </c>
+      <c r="AG6">
+        <v>-7.890000000000001</v>
+      </c>
+      <c r="AH6">
+        <v>0.0533910533910534</v>
+      </c>
+      <c r="AI6">
+        <v>0.1485943775100402</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.3167402649538339</v>
+      </c>
+      <c r="AK6">
+        <v>-2.911439114391145</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0314</v>
+        <v>0.00631</v>
       </c>
       <c r="E2">
-        <v>0.07519999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="G2">
-        <v>0.5480475382003396</v>
+        <v>0.182659355723098</v>
       </c>
       <c r="H2">
-        <v>0.5480475382003396</v>
+        <v>0.182659355723098</v>
       </c>
       <c r="I2">
-        <v>0.4254668930390493</v>
+        <v>0.1592186429061001</v>
       </c>
       <c r="J2">
-        <v>0.3294447926148162</v>
+        <v>0.1294314298053869</v>
       </c>
       <c r="K2">
-        <v>8.65</v>
+        <v>0.857</v>
       </c>
       <c r="L2">
-        <v>0.2937181663837012</v>
+        <v>0.05873886223440713</v>
       </c>
       <c r="M2">
-        <v>3.644</v>
+        <v>1.429</v>
       </c>
       <c r="N2">
-        <v>0.02831390831390831</v>
+        <v>0.02393634840871022</v>
       </c>
       <c r="O2">
-        <v>0.421271676300578</v>
+        <v>1.667444574095683</v>
       </c>
       <c r="P2">
-        <v>3.644</v>
+        <v>1.429</v>
       </c>
       <c r="Q2">
-        <v>0.02831390831390831</v>
+        <v>0.02393634840871022</v>
       </c>
       <c r="R2">
-        <v>0.421271676300578</v>
+        <v>1.667444574095683</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>62.33</v>
+        <v>24.52</v>
       </c>
       <c r="V2">
-        <v>0.4843045843045843</v>
+        <v>0.4107202680067002</v>
       </c>
       <c r="W2">
-        <v>0.06822981366459627</v>
+        <v>0.07857142857142858</v>
       </c>
       <c r="X2">
-        <v>0.1129821789850635</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="Y2">
-        <v>-0.04475236532046727</v>
+        <v>-0.0298428212123905</v>
       </c>
       <c r="Z2">
-        <v>0.4317548746518105</v>
+        <v>1.026019690576653</v>
       </c>
       <c r="AA2">
-        <v>0.1109594638882298</v>
+        <v>0.349214276625525</v>
       </c>
       <c r="AB2">
-        <v>0.1129821789850635</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="AC2">
-        <v>-0.002022715096833744</v>
+        <v>0.2408000268417059</v>
       </c>
       <c r="AD2">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-60.48</v>
+        <v>-24.52</v>
       </c>
       <c r="AH2">
-        <v>0.01417081577939487</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.01718532280538783</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.8865435356200527</v>
+        <v>-0.6969869243888575</v>
       </c>
       <c r="AK2">
-        <v>-1.334510150044131</v>
+        <v>-2.046744574290484</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AN2">
-        <v>0.1397280966767372</v>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>20.92792792792793</v>
       </c>
       <c r="AP2">
-        <v>-4.56797583081571</v>
+        <v>-9.169783096484668</v>
+      </c>
+      <c r="AQ2">
+        <v>20.92792792792793</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00285</v>
+        <v>0.00885</v>
       </c>
       <c r="E3">
-        <v>-0.0134</v>
+        <v>0.127</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.3092105263157894</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>0.3092105263157894</v>
       </c>
       <c r="I3">
-        <v>0.3381818181818182</v>
+        <v>0.2565789473684211</v>
       </c>
       <c r="J3">
-        <v>0.1934545454545455</v>
+        <v>0.180921052631579</v>
       </c>
       <c r="K3">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="L3">
-        <v>0.1945454545454545</v>
+        <v>0.180921052631579</v>
       </c>
       <c r="M3">
-        <v>0.573</v>
+        <v>0.441</v>
       </c>
       <c r="N3">
-        <v>0.03493902439024391</v>
+        <v>0.02863636363636364</v>
       </c>
       <c r="O3">
-        <v>0.5355140186915887</v>
+        <v>0.4009090909090909</v>
       </c>
       <c r="P3">
-        <v>0.573</v>
+        <v>0.441</v>
       </c>
       <c r="Q3">
-        <v>0.03493902439024391</v>
+        <v>0.02863636363636364</v>
       </c>
       <c r="R3">
-        <v>0.5355140186915887</v>
+        <v>0.4009090909090909</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,22 +770,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.9</v>
+        <v>13</v>
       </c>
       <c r="V3">
-        <v>0.9085365853658538</v>
+        <v>0.8441558441558441</v>
       </c>
       <c r="W3">
-        <v>0.06645962732919254</v>
+        <v>0.07857142857142858</v>
       </c>
       <c r="X3">
-        <v>0.1129821789850635</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="Y3">
-        <v>-0.04652255165587099</v>
+        <v>-0.0298428212123905</v>
       </c>
       <c r="AB3">
-        <v>0.1129821789850635</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-14.9</v>
+        <v>-13</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,10 +806,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-9.933333333333346</v>
+        <v>-5.416666666666666</v>
       </c>
       <c r="AK3">
-        <v>16.55555555555555</v>
+        <v>-26</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-7.163461538461538</v>
+        <v>-7.471264367816092</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Reliance Insurance Limited (DSE:RELIANCINS)</t>
+          <t>Bangladesh General Insurance Company Limited (DSE:BGIC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,46 +841,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0314</v>
+        <v>0.00631</v>
       </c>
       <c r="E4">
-        <v>0.07519999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="G4">
-        <v>0.5621621621621622</v>
+        <v>0.2413223140495868</v>
       </c>
       <c r="H4">
-        <v>0.5621621621621622</v>
+        <v>0.2413223140495868</v>
       </c>
       <c r="I4">
-        <v>0.4713513513513514</v>
+        <v>0.2132231404958678</v>
       </c>
       <c r="J4">
-        <v>0.3238499469446352</v>
+        <v>0.1564249073810202</v>
       </c>
       <c r="K4">
-        <v>5.95</v>
+        <v>0.847</v>
       </c>
       <c r="L4">
-        <v>0.3216216216216216</v>
+        <v>0.14</v>
       </c>
       <c r="M4">
-        <v>2.61</v>
+        <v>0.589</v>
       </c>
       <c r="N4">
-        <v>0.04371859296482412</v>
+        <v>0.02318897637795276</v>
       </c>
       <c r="O4">
-        <v>0.4386554621848739</v>
+        <v>0.6953955135773318</v>
       </c>
       <c r="P4">
-        <v>2.61</v>
+        <v>0.589</v>
       </c>
       <c r="Q4">
-        <v>0.04371859296482412</v>
+        <v>0.02318897637795276</v>
       </c>
       <c r="R4">
-        <v>0.4386554621848739</v>
+        <v>0.6953955135773318</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,31 +889,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>35.1</v>
+        <v>9.56</v>
       </c>
       <c r="V4">
-        <v>0.5879396984924623</v>
+        <v>0.3763779527559056</v>
       </c>
       <c r="W4">
-        <v>0.07000000000000001</v>
+        <v>0.0799056603773585</v>
       </c>
       <c r="X4">
-        <v>0.1129821789850635</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="Y4">
-        <v>-0.04298217898506353</v>
+        <v>-0.02850858940646059</v>
       </c>
       <c r="Z4">
-        <v>0.4166666666666667</v>
+        <v>2.232472324723248</v>
       </c>
       <c r="AA4">
-        <v>0.134937477893598</v>
+        <v>0.349214276625525</v>
       </c>
       <c r="AB4">
-        <v>0.1129821789850635</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="AC4">
-        <v>0.02195529890853447</v>
+        <v>0.2408000268417059</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -919,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-35.1</v>
+        <v>-9.56</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -928,22 +934,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-1.426829268292683</v>
+        <v>-0.6035353535353536</v>
       </c>
       <c r="AK4">
-        <v>-1.096875</v>
+        <v>-39.8333333333333</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>11.62162162162162</v>
+      </c>
       <c r="AP4">
-        <v>-3.852908891328211</v>
+        <v>-6.685314685314686</v>
+      </c>
+      <c r="AQ4">
+        <v>11.62162162162162</v>
       </c>
     </row>
     <row r="5">
@@ -963,46 +975,43 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0593</v>
-      </c>
-      <c r="E5">
-        <v>0.11</v>
+        <v>-0.0876</v>
       </c>
       <c r="G5">
-        <v>0.5486238532110091</v>
+        <v>-0.274390243902439</v>
       </c>
       <c r="H5">
-        <v>0.5486238532110091</v>
+        <v>-0.274390243902439</v>
       </c>
       <c r="I5">
-        <v>0.3577981651376146</v>
+        <v>-0.2142276422764228</v>
       </c>
       <c r="J5">
-        <v>0.299886503357609</v>
+        <v>-0.2142276422764228</v>
       </c>
       <c r="K5">
-        <v>1.63</v>
+        <v>-1.09</v>
       </c>
       <c r="L5">
-        <v>0.2990825688073394</v>
+        <v>-0.443089430894309</v>
       </c>
       <c r="M5">
-        <v>0.461</v>
+        <v>0.399</v>
       </c>
       <c r="N5">
-        <v>0.02328282828282828</v>
+        <v>0.02111111111111112</v>
       </c>
       <c r="O5">
-        <v>0.2828220858895706</v>
+        <v>-0.3660550458715596</v>
       </c>
       <c r="P5">
-        <v>0.461</v>
+        <v>0.399</v>
       </c>
       <c r="Q5">
-        <v>0.02328282828282828</v>
+        <v>0.02111111111111112</v>
       </c>
       <c r="R5">
-        <v>0.2828220858895706</v>
+        <v>-0.3660550458715596</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,31 +1020,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
-        <v>0.1308080808080808</v>
+        <v>0.1037037037037037</v>
       </c>
       <c r="W5">
-        <v>0.07546296296296295</v>
+        <v>-0.07730496453900711</v>
       </c>
       <c r="X5">
-        <v>0.1129821789850635</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="Y5">
-        <v>-0.03751921602210058</v>
+        <v>-0.1857192143228262</v>
       </c>
       <c r="Z5">
-        <v>0.2900478978179882</v>
+        <v>0.2137271937445699</v>
       </c>
       <c r="AA5">
-        <v>0.08698144988286158</v>
+        <v>-0.04578627280625543</v>
       </c>
       <c r="AB5">
-        <v>0.1129821789850635</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="AC5">
-        <v>-0.02600072910220196</v>
+        <v>-0.1542005225900745</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1047,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-2.59</v>
+        <v>-1.96</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1056,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.1504938988959907</v>
+        <v>-0.115702479338843</v>
       </c>
       <c r="AK5">
-        <v>-0.2250217202432667</v>
+        <v>-0.1743772241992883</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1068,102 +1077,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP5">
-        <v>-1.263414634146341</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bangladesh General Insurance Company Limited (DSE:BGIC)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>9.74</v>
-      </c>
-      <c r="V6">
-        <v>0.2969512195121952</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0.115806416668222</v>
-      </c>
-      <c r="Y6">
-        <v>-0.115806416668222</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.1133283771356361</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1133283771356361</v>
-      </c>
-      <c r="AD6">
-        <v>1.85</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>1.85</v>
-      </c>
-      <c r="AG6">
-        <v>-7.890000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.0533910533910534</v>
-      </c>
-      <c r="AI6">
-        <v>0.1485943775100402</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.3167402649538339</v>
-      </c>
-      <c r="AK6">
-        <v>-2.911439114391145</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
+        <v>3.951612903225806</v>
       </c>
     </row>
   </sheetData>
